--- a/exports/M&M_full_report.xlsx
+++ b/exports/M&M_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q72"/>
+  <dimension ref="A1:U72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>4.92</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>874</v>
+        <v>855.3</v>
       </c>
       <c r="I2" t="n">
         <v>859.8069949800479</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>3.83</v>
+        <v>1.61</v>
       </c>
       <c r="L2" t="n">
         <v>1.43</v>
@@ -555,7 +578,7 @@
         <v>0.74</v>
       </c>
       <c r="N2" t="n">
-        <v>1.33</v>
+        <v>2.13</v>
       </c>
       <c r="O2" t="n">
         <v>1.57</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>6.77</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44607.55208333334</v>
+        <v>44608.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>854.05</v>
+        <v>875.1</v>
       </c>
       <c r="I3" t="n">
         <v>873.4704977648462</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K3" t="n">
-        <v>0.15</v>
+        <v>-2.31</v>
       </c>
       <c r="L3" t="n">
         <v>4.76</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>8.42</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44616.38541666666</v>
+        <v>44616.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>810.4</v>
+        <v>796.6</v>
       </c>
       <c r="I4" t="n">
         <v>808.8165492850217</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.39</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>8.18</v>
+        <v>9.67</v>
       </c>
       <c r="M4" t="n">
         <v>3.73</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44634.55208333334</v>
+        <v>44635.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>744.9</v>
+        <v>758.35</v>
       </c>
       <c r="I5" t="n">
         <v>754.455821520829</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>6.49</v>
+        <v>4.8</v>
       </c>
       <c r="L5" t="n">
         <v>3.57</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,25 +833,25 @@
         <v>8.039999999999999</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44687.55208333334</v>
+        <v>44690.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>895.7</v>
+        <v>883</v>
       </c>
       <c r="I6" t="n">
         <v>884.2383046376822</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>52.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K6" t="n">
-        <v>18.11</v>
+        <v>16.44</v>
       </c>
       <c r="L6" t="n">
         <v>1.76</v>
       </c>
       <c r="M6" t="n">
-        <v>1.03</v>
+        <v>1.75</v>
       </c>
       <c r="N6" t="n">
         <v>2.4</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>6.32</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44701.55208333334</v>
+        <v>44704.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>904.9</v>
+        <v>935.8</v>
       </c>
       <c r="I7" t="n">
         <v>919.2397941918985</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.48</v>
+        <v>-5.98</v>
       </c>
       <c r="L7" t="n">
-        <v>4.5</v>
+        <v>6.31</v>
       </c>
       <c r="M7" t="n">
         <v>1.59</v>
       </c>
       <c r="N7" t="n">
-        <v>2.94</v>
+        <v>3.99</v>
       </c>
       <c r="O7" t="n">
         <v>-0.45</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.2</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44729.55208333334</v>
+        <v>44732.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>1000.4</v>
+        <v>987</v>
       </c>
       <c r="I8" t="n">
         <v>988.9475464219572</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K8" t="n">
-        <v>6.9</v>
+        <v>5.47</v>
       </c>
       <c r="L8" t="n">
         <v>2.65</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,25 +1040,25 @@
         <v>6.62</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44735.55208333334</v>
+        <v>44736.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>1029.9</v>
+        <v>1061.8</v>
       </c>
       <c r="I9" t="n">
         <v>1033.003554467883</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.35</v>
+        <v>-7.58</v>
       </c>
       <c r="L9" t="n">
-        <v>4.52</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>0.46</v>
+        <v>0.68</v>
       </c>
       <c r="N9" t="n">
         <v>4.7</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.42</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>1298.9</v>
+        <v>1245.45</v>
       </c>
       <c r="I10" t="n">
         <v>1257.925520357175</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>83.16666666666667</v>
+        <v>84</v>
       </c>
       <c r="K10" t="n">
-        <v>22.33</v>
+        <v>17.3</v>
       </c>
       <c r="L10" t="n">
         <v>2.84</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.56</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44859.55208333334</v>
+        <v>44861.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>1279.25</v>
+        <v>1287.7</v>
       </c>
       <c r="I11" t="n">
         <v>1287.603213578304</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.71</v>
+        <v>-3.39</v>
       </c>
       <c r="L11" t="n">
         <v>6.22</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>4.52</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44874.55208333334</v>
+        <v>44875.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>1334.7</v>
+        <v>1293.5</v>
       </c>
       <c r="I12" t="n">
         <v>1294.940389202936</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
-        <v>3.65</v>
+        <v>0.45</v>
       </c>
       <c r="L12" t="n">
         <v>0.67</v>
@@ -1125,7 +1268,7 @@
         <v>0.86</v>
       </c>
       <c r="N12" t="n">
-        <v>1.32</v>
+        <v>2.86</v>
       </c>
       <c r="O12" t="n">
         <v>1.23</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>6.62</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44894.55208333334</v>
+        <v>44895.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>1256.2</v>
+        <v>1284.85</v>
       </c>
       <c r="I13" t="n">
         <v>1280.076038419407</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>2.88</v>
+        <v>0.67</v>
       </c>
       <c r="L13" t="n">
         <v>3.52</v>
@@ -1182,7 +1337,7 @@
         <v>1.16</v>
       </c>
       <c r="N13" t="n">
-        <v>1.54</v>
+        <v>4.12</v>
       </c>
       <c r="O13" t="n">
         <v>-2.86</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>5.07</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44916.55208333334</v>
+        <v>44917.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>1265.95</v>
+        <v>1238.55</v>
       </c>
       <c r="I14" t="n">
         <v>1248.821728991307</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.47</v>
+        <v>-3.6</v>
       </c>
       <c r="L14" t="n">
-        <v>2.83</v>
+        <v>3.8</v>
       </c>
       <c r="M14" t="n">
         <v>0.85</v>
       </c>
       <c r="N14" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="O14" t="n">
         <v>4.12</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>6.07</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44932.55208333334</v>
+        <v>44935.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>1263.4</v>
+        <v>1308.7</v>
       </c>
       <c r="I15" t="n">
         <v>1276.906805036285</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.01</v>
+        <v>-5.66</v>
       </c>
       <c r="L15" t="n">
-        <v>3.13</v>
+        <v>6.08</v>
       </c>
       <c r="M15" t="n">
-        <v>0.51</v>
+        <v>0.76</v>
       </c>
       <c r="N15" t="n">
-        <v>1.96</v>
+        <v>3.7</v>
       </c>
       <c r="O15" t="n">
         <v>-2.49</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>5.9</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44979.55208333334</v>
+        <v>44980.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>1331</v>
+        <v>1312.7</v>
       </c>
       <c r="I16" t="n">
         <v>1315.20612418092</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7</v>
+        <v>0.31</v>
       </c>
       <c r="L16" t="n">
         <v>2.82</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.31</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45022.55208333334</v>
+        <v>45026.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>1171.95</v>
+        <v>1185</v>
       </c>
       <c r="I17" t="n">
         <v>1183.15041345323</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K17" t="n">
-        <v>10.72</v>
+        <v>9.73</v>
       </c>
       <c r="L17" t="n">
         <v>1.03</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>4.63</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45133.55208333334</v>
+        <v>45134.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>1545.9</v>
+        <v>1458.35</v>
       </c>
       <c r="I18" t="n">
         <v>1514.082762374306</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>107.1666666666667</v>
+        <v>108</v>
       </c>
       <c r="K18" t="n">
-        <v>30.46</v>
+        <v>23.07</v>
       </c>
       <c r="L18" t="n">
         <v>1.16</v>
       </c>
       <c r="M18" t="n">
-        <v>0.63</v>
+        <v>3.03</v>
       </c>
       <c r="N18" t="n">
-        <v>2.06</v>
+        <v>6.27</v>
       </c>
       <c r="O18" t="n">
         <v>1.45</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>150</v>
+        <v>151</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>6.85</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45147.55208333334</v>
+        <v>45148.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>1535</v>
+        <v>1545.25</v>
       </c>
       <c r="I19" t="n">
         <v>1540.446270883786</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.26</v>
+        <v>-5.96</v>
       </c>
       <c r="L19" t="n">
-        <v>5.43</v>
+        <v>6.7</v>
       </c>
       <c r="M19" t="n">
         <v>1.74</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>6.05</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45180.55208333334</v>
+        <v>45181.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>1580.55</v>
+        <v>1517</v>
       </c>
       <c r="I20" t="n">
         <v>1536.597703748667</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K20" t="n">
-        <v>2.28</v>
+        <v>-1.83</v>
       </c>
       <c r="L20" t="n">
         <v>2.4</v>
@@ -1581,7 +1820,7 @@
         <v>0.72</v>
       </c>
       <c r="N20" t="n">
-        <v>1.59</v>
+        <v>1.76</v>
       </c>
       <c r="O20" t="n">
         <v>0.63</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>6.71</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45184.55208333334</v>
+        <v>45187.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>1603</v>
+        <v>1638.8</v>
       </c>
       <c r="I21" t="n">
         <v>1613.012165174733</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.67</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>6.18</v>
+        <v>10.09</v>
       </c>
       <c r="M21" t="n">
         <v>0.73</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>5.36</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45196.55208333334</v>
+        <v>45197.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>1597</v>
+        <v>1556.1</v>
       </c>
       <c r="I22" t="n">
         <v>1559.572682064423</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.55</v>
+        <v>-5.05</v>
       </c>
       <c r="L22" t="n">
-        <v>4.44</v>
+        <v>5.15</v>
       </c>
       <c r="M22" t="n">
         <v>1.05</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>6.38</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45238.55208333334</v>
+        <v>45239.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>1486</v>
+        <v>1538</v>
       </c>
       <c r="I23" t="n">
         <v>1529.281560505601</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K23" t="n">
-        <v>4.5</v>
+        <v>1.16</v>
       </c>
       <c r="L23" t="n">
         <v>2.69</v>
@@ -1752,7 +2027,7 @@
         <v>2.66</v>
       </c>
       <c r="N23" t="n">
-        <v>1.72</v>
+        <v>4.31</v>
       </c>
       <c r="O23" t="n">
         <v>-2.67</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,25 +2075,25 @@
         <v>5.86</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45280.55208333334</v>
+        <v>45281.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1660</v>
+        <v>1638.7</v>
       </c>
       <c r="I24" t="n">
         <v>1641.036375717513</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K24" t="n">
-        <v>7.93</v>
+        <v>6.55</v>
       </c>
       <c r="L24" t="n">
         <v>3.29</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2</v>
+        <v>1.51</v>
       </c>
       <c r="N24" t="n">
         <v>2.33</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>4.96</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45287.55208333334</v>
+        <v>45288.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>1683</v>
+        <v>1708.25</v>
       </c>
       <c r="I25" t="n">
         <v>1707.066948004437</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.7</v>
+        <v>-4.24</v>
       </c>
       <c r="L25" t="n">
-        <v>3.24</v>
+        <v>4.53</v>
       </c>
       <c r="M25" t="n">
         <v>0.54</v>
       </c>
       <c r="N25" t="n">
-        <v>1.75</v>
+        <v>3.09</v>
       </c>
       <c r="O25" t="n">
         <v>-1.27</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>4.87</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45294.38541666666</v>
+        <v>45294.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>1663.15</v>
+        <v>1656.9</v>
       </c>
       <c r="I26" t="n">
         <v>1659.210925812017</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.64</v>
+        <v>-3.01</v>
       </c>
       <c r="L26" t="n">
         <v>3.52</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>4.76</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45322.55208333334</v>
+        <v>45323.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1657</v>
+        <v>1669.05</v>
       </c>
       <c r="I27" t="n">
         <v>1660.456901476662</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.01</v>
+        <v>-0.73</v>
       </c>
       <c r="L27" t="n">
-        <v>1.06</v>
+        <v>2.76</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>4.58</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45330.55208333334</v>
+        <v>45331.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1691.2</v>
+        <v>1644.85</v>
       </c>
       <c r="I28" t="n">
         <v>1652.071378278423</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K28" t="n">
-        <v>1.33</v>
+        <v>-1.45</v>
       </c>
       <c r="L28" t="n">
-        <v>1.41</v>
+        <v>2.46</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="N28" t="n">
-        <v>1.9</v>
+        <v>2.76</v>
       </c>
       <c r="O28" t="n">
         <v>-0.36</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>6.64</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45336.55208333334</v>
+        <v>45337.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1662</v>
+        <v>1776.4</v>
       </c>
       <c r="I29" t="n">
         <v>1731.70692844072</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.04</v>
+        <v>-8</v>
       </c>
       <c r="L29" t="n">
-        <v>2.73</v>
+        <v>8.08</v>
       </c>
       <c r="M29" t="n">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="N29" t="n">
-        <v>1.04</v>
+        <v>6.49</v>
       </c>
       <c r="O29" t="n">
         <v>-2.76</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>9.949999999999999</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45364.38541666666</v>
+        <v>45364.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>1873.45</v>
+        <v>1847.1</v>
       </c>
       <c r="I30" t="n">
         <v>1857.810088082819</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>5.46</v>
+        <v>3.98</v>
       </c>
       <c r="L30" t="n">
         <v>6.1</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>6.01</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45383.55208333334</v>
+        <v>45384.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1917</v>
+        <v>1945.85</v>
       </c>
       <c r="I31" t="n">
         <v>1922.166332569719</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.78</v>
+        <v>-5.35</v>
       </c>
       <c r="L31" t="n">
         <v>6.32</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>7.16</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45482.55208333334</v>
+        <v>45483.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>2920</v>
+        <v>2720.6</v>
       </c>
       <c r="I32" t="n">
         <v>2802.959203355339</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>98.16666666666667</v>
+        <v>99</v>
       </c>
       <c r="K32" t="n">
-        <v>50.06</v>
+        <v>39.82</v>
       </c>
       <c r="L32" t="n">
         <v>2.28</v>
@@ -2265,7 +2648,7 @@
         <v>1.56</v>
       </c>
       <c r="N32" t="n">
-        <v>2.16</v>
+        <v>6.51</v>
       </c>
       <c r="O32" t="n">
         <v>2.76</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>133</v>
+        <v>134</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>10.3</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45499.38541666666</v>
+        <v>45499.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>2851.95</v>
+        <v>2892</v>
       </c>
       <c r="I33" t="n">
         <v>2857.824707640151</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K33" t="n">
-        <v>-4.83</v>
+        <v>-6.3</v>
       </c>
       <c r="L33" t="n">
         <v>7.7</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,25 +2765,25 @@
         <v>5.69</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45505.55208333334</v>
+        <v>45506.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>2827</v>
+        <v>2752.3</v>
       </c>
       <c r="I34" t="n">
         <v>2790.289315532953</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.25</v>
+        <v>-4.83</v>
       </c>
       <c r="L34" t="n">
-        <v>2.49</v>
+        <v>4.84</v>
       </c>
       <c r="M34" t="n">
-        <v>0.05</v>
+        <v>0.59</v>
       </c>
       <c r="N34" t="n">
         <v>2.82</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>7.31</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45520.38541666666</v>
+        <v>45520.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>2819.3</v>
+        <v>2840</v>
       </c>
       <c r="I35" t="n">
         <v>2835.396303915413</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.43</v>
+        <v>-3.19</v>
       </c>
       <c r="L35" t="n">
-        <v>3.1</v>
+        <v>3.37</v>
       </c>
       <c r="M35" t="n">
         <v>2.01</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>5.3</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45540.55208333334</v>
+        <v>45541.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>2721</v>
+        <v>2694.8</v>
       </c>
       <c r="I36" t="n">
         <v>2706.04290144727</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>-4.19</v>
+        <v>-5.11</v>
       </c>
       <c r="L36" t="n">
-        <v>4.51</v>
+        <v>5.63</v>
       </c>
       <c r="M36" t="n">
         <v>0.79</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>4.65</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45548.55208333334</v>
+        <v>45551.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>2737.2</v>
+        <v>2775</v>
       </c>
       <c r="I37" t="n">
         <v>2758.641149794938</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.57</v>
+        <v>-2.98</v>
       </c>
       <c r="L37" t="n">
-        <v>2.37</v>
+        <v>3.32</v>
       </c>
       <c r="M37" t="n">
         <v>1.03</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>4.87</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45581.55208333334</v>
+        <v>45582.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>3068</v>
+        <v>2978.35</v>
       </c>
       <c r="I38" t="n">
         <v>3018.012743916419</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K38" t="n">
-        <v>10.56</v>
+        <v>7.33</v>
       </c>
       <c r="L38" t="n">
         <v>1.55</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>7.76</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45601.55208333334</v>
+        <v>45602.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>2890</v>
+        <v>2930</v>
       </c>
       <c r="I39" t="n">
         <v>2899.61929122588</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K39" t="n">
-        <v>2.97</v>
+        <v>1.62</v>
       </c>
       <c r="L39" t="n">
         <v>2.92</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.84</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45646.38541666666</v>
+        <v>45646.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>2942.25</v>
+        <v>2916.95</v>
       </c>
       <c r="I40" t="n">
         <v>2938.863195690209</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>44</v>
+        <v>44.16666666666666</v>
       </c>
       <c r="K40" t="n">
-        <v>0.42</v>
+        <v>-0.45</v>
       </c>
       <c r="L40" t="n">
         <v>6.61</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>5.18</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45652.55208333334</v>
+        <v>45653.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>2984.2</v>
+        <v>3054</v>
       </c>
       <c r="I41" t="n">
         <v>3045.709617073687</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.31</v>
+        <v>-4.7</v>
       </c>
       <c r="L41" t="n">
-        <v>2.31</v>
+        <v>4.9</v>
       </c>
       <c r="M41" t="n">
         <v>0.29</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>5.99</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45667.55208333334</v>
+        <v>45670.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>3090.45</v>
+        <v>3027.25</v>
       </c>
       <c r="I42" t="n">
         <v>3045.901473237499</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K42" t="n">
-        <v>1.19</v>
+        <v>-0.88</v>
       </c>
       <c r="L42" t="n">
         <v>2.71</v>
       </c>
       <c r="M42" t="n">
-        <v>0.7</v>
+        <v>1.19</v>
       </c>
       <c r="N42" t="n">
-        <v>2.64</v>
+        <v>2.93</v>
       </c>
       <c r="O42" t="n">
         <v>1.94</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>6.2</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45686.55208333334</v>
+        <v>45687.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>2933.5</v>
+        <v>3002.5</v>
       </c>
       <c r="I43" t="n">
         <v>2962.902259834661</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K43" t="n">
-        <v>3.1</v>
+        <v>0.82</v>
       </c>
       <c r="L43" t="n">
         <v>1.69</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>7.46</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45699.55208333334</v>
+        <v>45700.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>3085</v>
+        <v>3011.4</v>
       </c>
       <c r="I44" t="n">
         <v>3017.861126576358</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K44" t="n">
-        <v>2.75</v>
+        <v>0.3</v>
       </c>
       <c r="L44" t="n">
         <v>2.78</v>
       </c>
       <c r="M44" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="N44" t="n">
-        <v>1.95</v>
+        <v>3.17</v>
       </c>
       <c r="O44" t="n">
         <v>1.31</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>7.18</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45734.55208333334</v>
+        <v>45735.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>2790</v>
+        <v>2800.35</v>
       </c>
       <c r="I45" t="n">
         <v>2799.704380042909</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K45" t="n">
-        <v>7.35</v>
+        <v>7.01</v>
       </c>
       <c r="L45" t="n">
         <v>2.11</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>5.45</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45743.55208333334</v>
+        <v>45744.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>2734</v>
+        <v>2660</v>
       </c>
       <c r="I46" t="n">
         <v>2711.471767689984</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.37</v>
+        <v>-5.01</v>
       </c>
       <c r="L46" t="n">
-        <v>3.74</v>
+        <v>5.9</v>
       </c>
       <c r="M46" t="n">
         <v>0.26</v>
       </c>
       <c r="N46" t="n">
-        <v>1.79</v>
+        <v>2.71</v>
       </c>
       <c r="O46" t="n">
         <v>-0.18</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>7.53</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45763.55208333334</v>
+        <v>45764.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>2636.6</v>
+        <v>2675</v>
       </c>
       <c r="I47" t="n">
         <v>2665.273506013488</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K47" t="n">
-        <v>0.88</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="L47" t="n">
         <v>3</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>7.51</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45806.55208333334</v>
+        <v>45807.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>3013.6</v>
+        <v>2970.1</v>
       </c>
       <c r="I48" t="n">
         <v>2990.041789679882</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K48" t="n">
-        <v>12.66</v>
+        <v>11.03</v>
       </c>
       <c r="L48" t="n">
         <v>2.71</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>5.09</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45827.55208333334</v>
+        <v>45828.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>3089</v>
+        <v>3176.1</v>
       </c>
       <c r="I49" t="n">
         <v>3099.035549678796</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K49" t="n">
-        <v>-4</v>
+        <v>-6.94</v>
       </c>
       <c r="L49" t="n">
-        <v>5.75</v>
+        <v>7.2</v>
       </c>
       <c r="M49" t="n">
         <v>0.88</v>
       </c>
       <c r="N49" t="n">
-        <v>1.92</v>
+        <v>3.27</v>
       </c>
       <c r="O49" t="n">
         <v>-1.45</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>5.65</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45849.38541666666</v>
+        <v>45849.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>3086.1</v>
+        <v>3071</v>
       </c>
       <c r="I50" t="n">
         <v>3078.446268308132</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.83</v>
+        <v>-3.31</v>
       </c>
       <c r="L50" t="n">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="M50" t="n">
         <v>0.82</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>4.23</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45854.38541666666</v>
+        <v>45854.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>3123.3</v>
+        <v>3203</v>
       </c>
       <c r="I51" t="n">
         <v>3200.931236745717</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>4.833333333333333</v>
+        <v>5</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.7</v>
+        <v>-4.3</v>
       </c>
       <c r="L51" t="n">
-        <v>2.52</v>
+        <v>4.53</v>
       </c>
       <c r="M51" t="n">
         <v>0.06</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>5.53</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45897.55208333334</v>
+        <v>45898.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>3301</v>
+        <v>3200.8</v>
       </c>
       <c r="I52" t="n">
         <v>3279.163947631958</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>43</v>
+        <v>43.83333333333334</v>
       </c>
       <c r="K52" t="n">
-        <v>3.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L52" t="n">
         <v>2.69</v>
@@ -3405,7 +4028,7 @@
         <v>1.3</v>
       </c>
       <c r="N52" t="n">
-        <v>2.06</v>
+        <v>3.06</v>
       </c>
       <c r="O52" t="n">
         <v>2.17</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>5.92</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45903.55208333334</v>
+        <v>45904.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>3288</v>
+        <v>3489</v>
       </c>
       <c r="I53" t="n">
         <v>3349.758002979785</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.72</v>
+        <v>-9</v>
       </c>
       <c r="L53" t="n">
-        <v>4.04</v>
+        <v>10.91</v>
       </c>
       <c r="M53" t="n">
-        <v>0.96</v>
+        <v>7.27</v>
       </c>
       <c r="N53" t="n">
-        <v>3.5</v>
+        <v>5.84</v>
       </c>
       <c r="O53" t="n">
         <v>-3.06</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>6.09</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>3538.2</v>
+        <v>3420</v>
       </c>
       <c r="I54" t="n">
         <v>3512.115682595981</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K54" t="n">
-        <v>1.41</v>
+        <v>-1.98</v>
       </c>
       <c r="L54" t="n">
-        <v>0.73</v>
+        <v>2</v>
       </c>
       <c r="M54" t="n">
         <v>0.99</v>
       </c>
       <c r="N54" t="n">
-        <v>2.51</v>
+        <v>3.96</v>
       </c>
       <c r="O54" t="n">
         <v>5.84</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>6.63</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45946.55208333334</v>
+        <v>45947.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>3560</v>
+        <v>3628.1</v>
       </c>
       <c r="I55" t="n">
         <v>3561.951183291631</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K55" t="n">
-        <v>-4.09</v>
+        <v>-6.08</v>
       </c>
       <c r="L55" t="n">
-        <v>4.48</v>
+        <v>6.58</v>
       </c>
       <c r="M55" t="n">
         <v>0.7</v>
       </c>
       <c r="N55" t="n">
-        <v>1.98</v>
+        <v>2.62</v>
       </c>
       <c r="O55" t="n">
         <v>-3.96</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>4.49</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45959.55208333334</v>
+        <v>45960.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>3539.5</v>
+        <v>3510.6</v>
       </c>
       <c r="I56" t="n">
         <v>3512.696300155053</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.44</v>
+        <v>-3.24</v>
       </c>
       <c r="L56" t="n">
-        <v>2.92</v>
+        <v>3.64</v>
       </c>
       <c r="M56" t="n">
         <v>0.3</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,25 +4352,25 @@
         <v>3.82</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45965.55208333334</v>
+        <v>45967.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>3584.3</v>
+        <v>3643.8</v>
       </c>
       <c r="I57" t="n">
         <v>3606.782687626097</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.1</v>
+        <v>-3.79</v>
       </c>
       <c r="L57" t="n">
-        <v>3.48</v>
+        <v>4.67</v>
       </c>
       <c r="M57" t="n">
-        <v>0.58</v>
+        <v>1.14</v>
       </c>
       <c r="N57" t="n">
         <v>1.79</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>4.41</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46003.55208333334</v>
+        <v>46006.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>3680</v>
+        <v>3627.6</v>
       </c>
       <c r="I58" t="n">
         <v>3628.95198244319</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K58" t="n">
-        <v>0.99</v>
+        <v>-0.44</v>
       </c>
       <c r="L58" t="n">
         <v>2.11</v>
       </c>
       <c r="M58" t="n">
-        <v>0.57</v>
+        <v>1.3</v>
       </c>
       <c r="N58" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="O58" t="n">
         <v>0.86</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>3.75</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46022.38541666666</v>
+        <v>46022.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>3698.2</v>
+        <v>3716</v>
       </c>
       <c r="I59" t="n">
         <v>3699.543807761014</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.95</v>
+        <v>-2.44</v>
       </c>
       <c r="L59" t="n">
-        <v>2.02</v>
+        <v>2.65</v>
       </c>
       <c r="M59" t="n">
         <v>0.52</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>3.65</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46030.55208333334</v>
+        <v>46031.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>3715</v>
+        <v>3676.6</v>
       </c>
       <c r="I60" t="n">
         <v>3699.84415039032</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.03</v>
+        <v>-1.06</v>
       </c>
       <c r="L60" t="n">
-        <v>0.97</v>
+        <v>1.19</v>
       </c>
       <c r="M60" t="n">
         <v>0.67</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>4.69</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46056.55208333334</v>
+        <v>46057.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>3530</v>
+        <v>3590.6</v>
       </c>
       <c r="I61" t="n">
         <v>3570.312685178473</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K61" t="n">
-        <v>3.99</v>
+        <v>2.34</v>
       </c>
       <c r="L61" t="n">
         <v>1.96</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>8.25</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46066.55208333334</v>
+        <v>46069.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>3533</v>
+        <v>3473.8</v>
       </c>
       <c r="I62" t="n">
         <v>3516.982001543782</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.6</v>
+        <v>-3.25</v>
       </c>
       <c r="L62" t="n">
-        <v>1.99</v>
+        <v>3.26</v>
       </c>
       <c r="M62" t="n">
         <v>1.67</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>6.8</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46098.55208333334</v>
+        <v>46099.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>3122</v>
+        <v>3210.4</v>
       </c>
       <c r="I63" t="n">
         <v>3150.234504535583</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K63" t="n">
-        <v>10.13</v>
+        <v>7.58</v>
       </c>
       <c r="L63" t="n">
         <v>2.18</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>7.74</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46101.55208333334</v>
+        <v>46104.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>3075</v>
+        <v>2936.7</v>
       </c>
       <c r="I64" t="n">
         <v>3010.745090375105</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K64" t="n">
-        <v>-4.22</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>5.54</v>
+        <v>8.58</v>
       </c>
       <c r="M64" t="n">
         <v>2.36</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>3013</v>
+        <v>3207.3</v>
       </c>
       <c r="I65" t="n">
         <v>3177.871635225964</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K65" t="n">
-        <v>-2.6</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>7.53</v>
+        <v>10.02</v>
       </c>
       <c r="M65" t="n">
         <v>3.91</v>
       </c>
       <c r="N65" t="n">
-        <v>3.05</v>
+        <v>6.62</v>
       </c>
       <c r="O65" t="n">
         <v>-4.03</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>8.75</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46134.55208333334</v>
+        <v>46135.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>3150</v>
+        <v>3058.6</v>
       </c>
       <c r="I66" t="n">
         <v>3092.379710288328</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K66" t="n">
-        <v>-1.79</v>
+        <v>-4.64</v>
       </c>
       <c r="L66" t="n">
-        <v>3.06</v>
+        <v>4.78</v>
       </c>
       <c r="M66" t="n">
         <v>2.19</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>6.42</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46147.38541666666</v>
+        <v>46147.55208333334</v>
       </c>
       <c r="H67" t="n">
-        <v>3174.2</v>
+        <v>3220.8</v>
       </c>
       <c r="I67" t="n">
         <v>3200.903338834661</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K67" t="n">
-        <v>-3.78</v>
+        <v>-5.3</v>
       </c>
       <c r="L67" t="n">
-        <v>4.36</v>
+        <v>5.34</v>
       </c>
       <c r="M67" t="n">
         <v>1.21</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>7.24</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46154.55208333334</v>
+        <v>46155.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>3189.6</v>
+        <v>3157</v>
       </c>
       <c r="I68" t="n">
         <v>3183.381094978963</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.97</v>
+        <v>-1.98</v>
       </c>
       <c r="L68" t="n">
-        <v>2.51</v>
+        <v>3.19</v>
       </c>
       <c r="M68" t="n">
         <v>2.9</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>5.89</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>3039.9</v>
+        <v>3160</v>
       </c>
       <c r="I69" t="n">
         <v>3112.564324792359</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K69" t="n">
-        <v>3.71</v>
+        <v>-0.1</v>
       </c>
       <c r="L69" t="n">
         <v>1.03</v>
       </c>
       <c r="M69" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="N69" t="n">
-        <v>1.92</v>
+        <v>3.1</v>
       </c>
       <c r="O69" t="n">
         <v>-1.96</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>6.91</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46261.38541666666</v>
+        <v>46261.55208333334</v>
       </c>
       <c r="H70" t="n">
-        <v>3370</v>
+        <v>3342.1</v>
       </c>
       <c r="I70" t="n">
         <v>3365.240193228563</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>73</v>
+        <v>73.16666666666667</v>
       </c>
       <c r="K70" t="n">
-        <v>6.65</v>
+        <v>5.76</v>
       </c>
       <c r="L70" t="n">
         <v>4.27</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>4</v>
+      </c>
+      <c r="U70" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>3.57</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46310.55208333334</v>
+        <v>46311.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>2849.7</v>
+        <v>2921.6</v>
       </c>
       <c r="I71" t="n">
         <v>2860.843022464326</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>49</v>
+        <v>49.83333333333334</v>
       </c>
       <c r="K71" t="n">
-        <v>14.73</v>
+        <v>12.58</v>
       </c>
       <c r="L71" t="n">
         <v>0.89</v>
@@ -4488,7 +5339,7 @@
         <v>0.96</v>
       </c>
       <c r="N71" t="n">
-        <v>1.76</v>
+        <v>2.36</v>
       </c>
       <c r="O71" t="n">
         <v>-2.13</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4548,6 +5411,12 @@
       <c r="Q72" t="n">
         <v>14</v>
       </c>
+      <c r="R72" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6650,7 +7519,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.7</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="6">
@@ -6660,7 +7529,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.5</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="7">
@@ -6670,7 +7539,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>107.2</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8">
@@ -6680,7 +7549,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -6690,7 +7559,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.2</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="10">
@@ -6700,7 +7569,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="11">
@@ -6740,7 +7609,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.35</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="15">
@@ -6750,7 +7619,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.49</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="16">
@@ -6760,7 +7629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.21</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="17">
@@ -6770,7 +7639,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>50.06</v>
+        <v>39.82</v>
       </c>
     </row>
     <row r="18">
@@ -6780,7 +7649,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48.6</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="19">
@@ -6790,7 +7659,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.27</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="20">
@@ -6800,7 +7669,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.84</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="21">
@@ -6810,7 +7679,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.18</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="22">
@@ -6820,7 +7689,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -6830,7 +7699,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -6840,7 +7709,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="25">
@@ -6850,7 +7719,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.27</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="26">
@@ -6860,7 +7729,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.65</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="27">
@@ -6870,7 +7739,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.26</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="28">
@@ -6880,7 +7749,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
